--- a/output/Amazon_Seller_Master_Data.xlsx
+++ b/output/Amazon_Seller_Master_Data.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Amazon Sellers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Amazon Sellers" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Amazon Sellers'!$A$1:$U$392</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Amazon Sellers'!$A$1:$U$400</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U392"/>
+  <dimension ref="A1:U400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -38540,8 +38540,784 @@
         </is>
       </c>
     </row>
+    <row r="393">
+      <c r="A393" s="3" t="inlineStr">
+        <is>
+          <t>Slipper Racks</t>
+        </is>
+      </c>
+      <c r="B393" s="3" t="inlineStr"/>
+      <c r="C393" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D393" s="3" t="inlineStr">
+        <is>
+          <t>KSP HOME®</t>
+        </is>
+      </c>
+      <c r="E393" s="3" t="inlineStr">
+        <is>
+          <t>Marketplace Seller</t>
+        </is>
+      </c>
+      <c r="F393" s="3" t="inlineStr">
+        <is>
+          <t>Slipper Racks</t>
+        </is>
+      </c>
+      <c r="G393" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="H393" s="5" t="inlineStr">
+        <is>
+          <t>+919899199769</t>
+        </is>
+      </c>
+      <c r="I393" s="3" t="inlineStr">
+        <is>
+          <t>info@kspinc.in</t>
+        </is>
+      </c>
+      <c r="J393" s="5" t="inlineStr">
+        <is>
+          <t>27ABCDE1234F1Z5</t>
+        </is>
+      </c>
+      <c r="K393" s="5" t="inlineStr">
+        <is>
+          <t>ABCDE1234F</t>
+        </is>
+      </c>
+      <c r="L393" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M393" s="6" t="inlineStr">
+        <is>
+          <t>b 36 phase ii, noida dadri road, phase 2, uttar pradesh 201305</t>
+        </is>
+      </c>
+      <c r="N393" s="3" t="inlineStr"/>
+      <c r="O393" s="3" t="inlineStr">
+        <is>
+          <t>noida dadri road</t>
+        </is>
+      </c>
+      <c r="P393" s="3" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
+      <c r="Q393" s="5" t="inlineStr">
+        <is>
+          <t>201305</t>
+        </is>
+      </c>
+      <c r="R393" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S393" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="T393" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U393" s="3" t="inlineStr">
+        <is>
+          <t>Amazon.in Marketplace</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="3" t="inlineStr">
+        <is>
+          <t>Slipper Racks</t>
+        </is>
+      </c>
+      <c r="B394" s="3" t="inlineStr"/>
+      <c r="C394" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D394" s="3" t="inlineStr">
+        <is>
+          <t>Devam Trading Impex</t>
+        </is>
+      </c>
+      <c r="E394" s="3" t="inlineStr">
+        <is>
+          <t>Marketplace Seller</t>
+        </is>
+      </c>
+      <c r="F394" s="3" t="inlineStr">
+        <is>
+          <t>Slipper Racks</t>
+        </is>
+      </c>
+      <c r="G394" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="H394" s="5" t="inlineStr">
+        <is>
+          <t>+919726107013</t>
+        </is>
+      </c>
+      <c r="I394" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="J394" s="5" t="inlineStr">
+        <is>
+          <t>07FUQPK3330E1ZM</t>
+        </is>
+      </c>
+      <c r="K394" s="5" t="inlineStr">
+        <is>
+          <t>FUQPK3330E</t>
+        </is>
+      </c>
+      <c r="L394" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M394" s="6" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="N394" s="3" t="inlineStr"/>
+      <c r="O394" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="P394" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="Q394" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="R394" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S394" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="T394" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U394" s="3" t="inlineStr">
+        <is>
+          <t>Amazon.in Marketplace</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="3" t="inlineStr">
+        <is>
+          <t>Slipper Racks</t>
+        </is>
+      </c>
+      <c r="B395" s="3" t="inlineStr"/>
+      <c r="C395" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D395" s="3" t="inlineStr">
+        <is>
+          <t>STELITE</t>
+        </is>
+      </c>
+      <c r="E395" s="3" t="inlineStr">
+        <is>
+          <t>Marketplace Seller</t>
+        </is>
+      </c>
+      <c r="F395" s="3" t="inlineStr">
+        <is>
+          <t>Slipper Racks</t>
+        </is>
+      </c>
+      <c r="G395" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="H395" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="I395" s="3" t="inlineStr">
+        <is>
+          <t>support@fnshiftsolutions.com</t>
+        </is>
+      </c>
+      <c r="J395" s="5" t="inlineStr">
+        <is>
+          <t>27ABDCS5646R1ZI</t>
+        </is>
+      </c>
+      <c r="K395" s="5" t="inlineStr">
+        <is>
+          <t>ABDCS5646R</t>
+        </is>
+      </c>
+      <c r="L395" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M395" s="6" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="N395" s="3" t="inlineStr"/>
+      <c r="O395" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="P395" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="Q395" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="R395" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S395" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="T395" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U395" s="3" t="inlineStr">
+        <is>
+          <t>Amazon.in Marketplace</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="3" t="inlineStr">
+        <is>
+          <t>Bar Tables</t>
+        </is>
+      </c>
+      <c r="B396" s="3" t="inlineStr"/>
+      <c r="C396" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D396" s="3" t="inlineStr">
+        <is>
+          <t>PRITI INTERNATIONAL LTD</t>
+        </is>
+      </c>
+      <c r="E396" s="3" t="inlineStr">
+        <is>
+          <t>Marketplace Seller</t>
+        </is>
+      </c>
+      <c r="F396" s="3" t="inlineStr">
+        <is>
+          <t>Bar Tables</t>
+        </is>
+      </c>
+      <c r="G396" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="H396" s="5" t="inlineStr">
+        <is>
+          <t>+919830082815</t>
+        </is>
+      </c>
+      <c r="I396" s="3" t="inlineStr">
+        <is>
+          <t>contact@pritiinternationalltd.com</t>
+        </is>
+      </c>
+      <c r="J396" s="5" t="inlineStr">
+        <is>
+          <t>08AAJCP2782Q1ZK</t>
+        </is>
+      </c>
+      <c r="K396" s="5" t="inlineStr">
+        <is>
+          <t>AAJCP2782Q</t>
+        </is>
+      </c>
+      <c r="L396" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M396" s="6" t="inlineStr">
+        <is>
+          <t>express zone a wing, 10th floor, western express highway, goregaon east, mumbai 400063.</t>
+        </is>
+      </c>
+      <c r="N396" s="3" t="inlineStr"/>
+      <c r="O396" s="3" t="inlineStr">
+        <is>
+          <t>mumbai .</t>
+        </is>
+      </c>
+      <c r="P396" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="Q396" s="5" t="inlineStr">
+        <is>
+          <t>400063</t>
+        </is>
+      </c>
+      <c r="R396" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S396" s="3" t="inlineStr">
+        <is>
+          <t>https://www.pritiinternationalltd.com/</t>
+        </is>
+      </c>
+      <c r="T396" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U396" s="3" t="inlineStr">
+        <is>
+          <t>Amazon.in Marketplace</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="3" t="inlineStr">
+        <is>
+          <t>Bar Tables</t>
+        </is>
+      </c>
+      <c r="B397" s="3" t="inlineStr"/>
+      <c r="C397" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D397" s="3" t="inlineStr">
+        <is>
+          <t>Furniture Factory Outlet</t>
+        </is>
+      </c>
+      <c r="E397" s="3" t="inlineStr">
+        <is>
+          <t>Marketplace Seller</t>
+        </is>
+      </c>
+      <c r="F397" s="3" t="inlineStr">
+        <is>
+          <t>Bar Tables</t>
+        </is>
+      </c>
+      <c r="G397" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="H397" s="5" t="inlineStr">
+        <is>
+          <t>+919846180055</t>
+        </is>
+      </c>
+      <c r="I397" s="3" t="inlineStr">
+        <is>
+          <t>contact@jaagrukbharat.com</t>
+        </is>
+      </c>
+      <c r="J397" s="5" t="inlineStr">
+        <is>
+          <t>27AAPFU0939F1ZV</t>
+        </is>
+      </c>
+      <c r="K397" s="5" t="inlineStr">
+        <is>
+          <t>AAPFU0939F</t>
+        </is>
+      </c>
+      <c r="L397" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M397" s="6" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="N397" s="3" t="inlineStr"/>
+      <c r="O397" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="P397" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="Q397" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="R397" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S397" s="3" t="inlineStr">
+        <is>
+          <t>https://www.furniturefactoryoutlet.in/</t>
+        </is>
+      </c>
+      <c r="T397" s="3" t="inlineStr">
+        <is>
+          <t>Partially Verified</t>
+        </is>
+      </c>
+      <c r="U397" s="3" t="inlineStr">
+        <is>
+          <t>Amazon.in Marketplace</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="3" t="inlineStr">
+        <is>
+          <t>Bar Tables</t>
+        </is>
+      </c>
+      <c r="B398" s="3" t="inlineStr"/>
+      <c r="C398" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D398" s="3" t="inlineStr">
+        <is>
+          <t>MTANK</t>
+        </is>
+      </c>
+      <c r="E398" s="3" t="inlineStr">
+        <is>
+          <t>Marketplace Seller</t>
+        </is>
+      </c>
+      <c r="F398" s="3" t="inlineStr">
+        <is>
+          <t>Bar Tables</t>
+        </is>
+      </c>
+      <c r="G398" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="H398" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="I398" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="J398" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="K398" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="L398" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M398" s="6" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="N398" s="3" t="inlineStr"/>
+      <c r="O398" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="P398" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="Q398" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="R398" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S398" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="T398" s="3" t="inlineStr">
+        <is>
+          <t>Partially Verified</t>
+        </is>
+      </c>
+      <c r="U398" s="3" t="inlineStr">
+        <is>
+          <t>Amazon.in Marketplace</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="3" t="inlineStr">
+        <is>
+          <t>Beds</t>
+        </is>
+      </c>
+      <c r="B399" s="3" t="inlineStr"/>
+      <c r="C399" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D399" s="3" t="inlineStr">
+        <is>
+          <t>RetailEZ Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="E399" s="3" t="inlineStr">
+        <is>
+          <t>Marketplace Seller</t>
+        </is>
+      </c>
+      <c r="F399" s="3" t="inlineStr">
+        <is>
+          <t>Beds</t>
+        </is>
+      </c>
+      <c r="G399" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="H399" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="I399" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="J399" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="K399" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="L399" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M399" s="6" t="inlineStr">
+        <is>
+          <t>yet you... I ordered this trolly bag from you delivered was schedule for Sept 8 or 9 but the status still shows delivered issued . ' I provided the correct address yet you haven't delivered my product . This is terrible😖 Read more Read less By Amazon Customer on 14 September, 2026. Message from Amazon: This item was fulfilled by Amazon, and we take responsibility for this fulfillment experience. 1 out of 5 stars One cap from bottle is missing By Bhanu on 14 September, 2026. 0 out of 5 stars template-truncated-text template-expanded-text Read more Read less By template-rater on template-date. Message from Amazon: template-suppress-reason-text template-response-truncated-text template-response-expanded-text Read more Read less By RetailEZ Pvt Ltd on template-response-date. Message from Amazon: template-suppress-reason-text Previous Previous Next Next Return and Refund Policies Please refer to the Amazon.in Return Policy . Shipping Policies Other Policies Help Products See all products currently offered by the seller. truncated-title product-total-priceproduct-price-currencyproduct-price-wholeproduct-price-decimalproduct-price-fraction product-total-priceproduct-price-wholeproduct-price-decimalproduct-price-fractionproduct-price-currency Leave seller feedback Skip to Main content Keyboard shortcuts Search alt + / Cart shift + alt + C Home shift + alt + H Orders shift + alt + O Show/Hide shortcuts shift + alt + Z To move between items, use your keyboard's up or down arrows. .in Delivering to Mumbai 400001 Update location All All Categories Alexa Skills Amazon Devices Amazon Fashion Amazon Fresh Meat Amazon Pharmacy Appliances Apps &amp; Games Audible Audiobooks Baby Beauty Books Car &amp; Motorbike Clothing &amp; Accessories Collectibles Computers &amp; Accessories Deals Electronics Furniture Garden &amp; Outdoors Gift Cards Grocery &amp; Gourmet Foods Health &amp; Personal Care Home &amp; Kitchen Industrial &amp; Scientific Jewellery Kindle Store Luggage &amp; Bags Luxury Beauty Movies &amp; TV Shows MP3 Music Music Musical Instruments Office Products Pet Supplies Prime Video Shoes &amp; Handbags Software Sports, Fitness &amp; Outdoors Subscribe &amp; Save Tools &amp; Home Improvement Toys &amp; Games Under ₹500 Video Games Watches EN Hello, sign in Account &amp; Lists Returns &amp; Orders 0 Cart All Fresh Meat Prime Video Sell Bestsellers Today's Deals Mobiles</t>
+        </is>
+      </c>
+      <c r="N399" s="3" t="inlineStr"/>
+      <c r="O399" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="P399" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="Q399" s="5" t="inlineStr">
+        <is>
+          <t>400001</t>
+        </is>
+      </c>
+      <c r="R399" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S399" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="T399" s="3" t="inlineStr">
+        <is>
+          <t>Partially Verified</t>
+        </is>
+      </c>
+      <c r="U399" s="3" t="inlineStr">
+        <is>
+          <t>Amazon.in Marketplace</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="3" t="inlineStr">
+        <is>
+          <t>Beds</t>
+        </is>
+      </c>
+      <c r="B400" s="3" t="inlineStr"/>
+      <c r="C400" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D400" s="3" t="inlineStr">
+        <is>
+          <t>Caspian Mumbai</t>
+        </is>
+      </c>
+      <c r="E400" s="3" t="inlineStr">
+        <is>
+          <t>Marketplace Seller</t>
+        </is>
+      </c>
+      <c r="F400" s="3" t="inlineStr">
+        <is>
+          <t>Beds</t>
+        </is>
+      </c>
+      <c r="G400" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="H400" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="I400" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="J400" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="K400" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="L400" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M400" s="6" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="N400" s="3" t="inlineStr"/>
+      <c r="O400" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="P400" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="Q400" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="R400" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S400" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="T400" s="3" t="inlineStr">
+        <is>
+          <t>Partially Verified</t>
+        </is>
+      </c>
+      <c r="U400" s="3" t="inlineStr">
+        <is>
+          <t>Amazon.in Marketplace</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U392"/>
+  <autoFilter ref="A1:U400"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
 </worksheet>

--- a/output/Amazon_Seller_Master_Data.xlsx
+++ b/output/Amazon_Seller_Master_Data.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Amazon Sellers" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Amazon Sellers'!$A$1:$U$400</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Amazon Sellers'!$A$1:$U$408</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U400"/>
+  <dimension ref="A1:U408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -39316,8 +39316,784 @@
         </is>
       </c>
     </row>
+    <row r="401">
+      <c r="A401" s="3" t="inlineStr">
+        <is>
+          <t>Benches</t>
+        </is>
+      </c>
+      <c r="B401" s="3" t="inlineStr"/>
+      <c r="C401" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D401" s="3" t="inlineStr">
+        <is>
+          <t>VIKASH-INDUSTRIES</t>
+        </is>
+      </c>
+      <c r="E401" s="3" t="inlineStr">
+        <is>
+          <t>Marketplace Seller</t>
+        </is>
+      </c>
+      <c r="F401" s="3" t="inlineStr">
+        <is>
+          <t>Benches</t>
+        </is>
+      </c>
+      <c r="G401" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="H401" s="5" t="inlineStr">
+        <is>
+          <t>+917004247461</t>
+        </is>
+      </c>
+      <c r="I401" s="3" t="inlineStr">
+        <is>
+          <t>info@vikashgroup.com</t>
+        </is>
+      </c>
+      <c r="J401" s="5" t="inlineStr">
+        <is>
+          <t>24AAEFV2547D1ZF</t>
+        </is>
+      </c>
+      <c r="K401" s="5" t="inlineStr">
+        <is>
+          <t>AAEFV2547D</t>
+        </is>
+      </c>
+      <c r="L401" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M401" s="6" t="inlineStr">
+        <is>
+          <t>ground floor, urbanvault, pice hq, 1350, 17th cross rd, parangi palaya, sector 2, hsr layout, bengaluru, karnataka 560102</t>
+        </is>
+      </c>
+      <c r="N401" s="3" t="inlineStr"/>
+      <c r="O401" s="3" t="inlineStr">
+        <is>
+          <t>bengaluru</t>
+        </is>
+      </c>
+      <c r="P401" s="3" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="Q401" s="5" t="inlineStr">
+        <is>
+          <t>560102</t>
+        </is>
+      </c>
+      <c r="R401" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S401" s="3" t="inlineStr">
+        <is>
+          <t>https://www.vikashindustries.com/</t>
+        </is>
+      </c>
+      <c r="T401" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U401" s="3" t="inlineStr">
+        <is>
+          <t>Amazon.in Marketplace</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="3" t="inlineStr">
+        <is>
+          <t>Cabinets &amp; Sideboards</t>
+        </is>
+      </c>
+      <c r="B402" s="3" t="inlineStr"/>
+      <c r="C402" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D402" s="3" t="inlineStr">
+        <is>
+          <t>RetailEZ Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="E402" s="3" t="inlineStr">
+        <is>
+          <t>Marketplace Seller</t>
+        </is>
+      </c>
+      <c r="F402" s="3" t="inlineStr">
+        <is>
+          <t>Cabinets &amp; Sideboards</t>
+        </is>
+      </c>
+      <c r="G402" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="H402" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="I402" s="3" t="inlineStr">
+        <is>
+          <t>support@tofler.in</t>
+        </is>
+      </c>
+      <c r="J402" s="5" t="inlineStr">
+        <is>
+          <t>06AALCR3173P1ZR</t>
+        </is>
+      </c>
+      <c r="K402" s="5" t="inlineStr">
+        <is>
+          <t>AALCR3173P</t>
+        </is>
+      </c>
+      <c r="L402" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M402" s="6" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="N402" s="3" t="inlineStr"/>
+      <c r="O402" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="P402" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="Q402" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="R402" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S402" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="T402" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U402" s="3" t="inlineStr">
+        <is>
+          <t>Amazon.in Marketplace</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="3" t="inlineStr">
+        <is>
+          <t>Dining Room Sets</t>
+        </is>
+      </c>
+      <c r="B403" s="3" t="inlineStr"/>
+      <c r="C403" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D403" s="3" t="inlineStr">
+        <is>
+          <t>AADITYA WOODS</t>
+        </is>
+      </c>
+      <c r="E403" s="3" t="inlineStr">
+        <is>
+          <t>Marketplace Seller</t>
+        </is>
+      </c>
+      <c r="F403" s="3" t="inlineStr">
+        <is>
+          <t>Dining Room Sets</t>
+        </is>
+      </c>
+      <c r="G403" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="H403" s="5" t="inlineStr">
+        <is>
+          <t>+918690327995</t>
+        </is>
+      </c>
+      <c r="I403" s="3" t="inlineStr">
+        <is>
+          <t>aadityawoods995@gmail.com</t>
+        </is>
+      </c>
+      <c r="J403" s="5" t="inlineStr">
+        <is>
+          <t>27AAPFU0939F1ZV</t>
+        </is>
+      </c>
+      <c r="K403" s="5" t="inlineStr">
+        <is>
+          <t>AAPFU0939F</t>
+        </is>
+      </c>
+      <c r="L403" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M403" s="6" t="inlineStr">
+        <is>
+          <t>Aaditya Woods, Plot No G-102 Road No. 02 Riico Industrial Area</t>
+        </is>
+      </c>
+      <c r="N403" s="3" t="inlineStr"/>
+      <c r="O403" s="3" t="inlineStr">
+        <is>
+          <t>Aaditya Woods</t>
+        </is>
+      </c>
+      <c r="P403" s="3" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="Q403" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="R403" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S403" s="3" t="inlineStr">
+        <is>
+          <t>https://www.aadityawoods.com/</t>
+        </is>
+      </c>
+      <c r="T403" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U403" s="3" t="inlineStr">
+        <is>
+          <t>Amazon.in Marketplace</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="3" t="inlineStr">
+        <is>
+          <t>Dressing Tables</t>
+        </is>
+      </c>
+      <c r="B404" s="3" t="inlineStr"/>
+      <c r="C404" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D404" s="3" t="inlineStr">
+        <is>
+          <t>NEUDOT</t>
+        </is>
+      </c>
+      <c r="E404" s="3" t="inlineStr">
+        <is>
+          <t>Marketplace Seller</t>
+        </is>
+      </c>
+      <c r="F404" s="3" t="inlineStr">
+        <is>
+          <t>Dressing Tables</t>
+        </is>
+      </c>
+      <c r="G404" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="H404" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="I404" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="J404" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="K404" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="L404" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M404" s="6" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="N404" s="3" t="inlineStr"/>
+      <c r="O404" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="P404" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="Q404" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="R404" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S404" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="T404" s="3" t="inlineStr">
+        <is>
+          <t>Partially Verified</t>
+        </is>
+      </c>
+      <c r="U404" s="3" t="inlineStr">
+        <is>
+          <t>Amazon.in Marketplace</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="3" t="inlineStr">
+        <is>
+          <t>Dressing Tables</t>
+        </is>
+      </c>
+      <c r="B405" s="3" t="inlineStr"/>
+      <c r="C405" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D405" s="3" t="inlineStr">
+        <is>
+          <t>Caspian Mumbai</t>
+        </is>
+      </c>
+      <c r="E405" s="3" t="inlineStr">
+        <is>
+          <t>Marketplace Seller</t>
+        </is>
+      </c>
+      <c r="F405" s="3" t="inlineStr">
+        <is>
+          <t>Dressing Tables</t>
+        </is>
+      </c>
+      <c r="G405" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="H405" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="I405" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="J405" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="K405" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="L405" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M405" s="6" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="N405" s="3" t="inlineStr"/>
+      <c r="O405" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="P405" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="Q405" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="R405" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S405" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="T405" s="3" t="inlineStr">
+        <is>
+          <t>Partially Verified</t>
+        </is>
+      </c>
+      <c r="U405" s="3" t="inlineStr">
+        <is>
+          <t>Amazon.in Marketplace</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="3" t="inlineStr">
+        <is>
+          <t>Box Springs</t>
+        </is>
+      </c>
+      <c r="B406" s="3" t="inlineStr"/>
+      <c r="C406" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D406" s="3" t="inlineStr">
+        <is>
+          <t>N.S. AUTOMOBILES.</t>
+        </is>
+      </c>
+      <c r="E406" s="3" t="inlineStr">
+        <is>
+          <t>Marketplace Seller</t>
+        </is>
+      </c>
+      <c r="F406" s="3" t="inlineStr">
+        <is>
+          <t>Box Springs</t>
+        </is>
+      </c>
+      <c r="G406" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="H406" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="I406" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="J406" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="K406" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="L406" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M406" s="6" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="N406" s="3" t="inlineStr"/>
+      <c r="O406" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="P406" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="Q406" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="R406" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S406" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="T406" s="3" t="inlineStr">
+        <is>
+          <t>Partially Verified</t>
+        </is>
+      </c>
+      <c r="U406" s="3" t="inlineStr">
+        <is>
+          <t>Amazon.in Marketplace</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="3" t="inlineStr">
+        <is>
+          <t>Box Springs</t>
+        </is>
+      </c>
+      <c r="B407" s="3" t="inlineStr"/>
+      <c r="C407" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D407" s="3" t="inlineStr">
+        <is>
+          <t>LEMBOSE BRAND</t>
+        </is>
+      </c>
+      <c r="E407" s="3" t="inlineStr">
+        <is>
+          <t>Marketplace Seller</t>
+        </is>
+      </c>
+      <c r="F407" s="3" t="inlineStr">
+        <is>
+          <t>Box Springs</t>
+        </is>
+      </c>
+      <c r="G407" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="H407" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="I407" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="J407" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="K407" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="L407" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M407" s="6" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="N407" s="3" t="inlineStr"/>
+      <c r="O407" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="P407" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="Q407" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="R407" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S407" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="T407" s="3" t="inlineStr">
+        <is>
+          <t>Partially Verified</t>
+        </is>
+      </c>
+      <c r="U407" s="3" t="inlineStr">
+        <is>
+          <t>Amazon.in Marketplace</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="3" t="inlineStr">
+        <is>
+          <t>Footboards</t>
+        </is>
+      </c>
+      <c r="B408" s="3" t="inlineStr"/>
+      <c r="C408" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D408" s="3" t="inlineStr">
+        <is>
+          <t>HCM AUTOMOTIVE PARTS</t>
+        </is>
+      </c>
+      <c r="E408" s="3" t="inlineStr">
+        <is>
+          <t>Marketplace Seller</t>
+        </is>
+      </c>
+      <c r="F408" s="3" t="inlineStr">
+        <is>
+          <t>Footboards</t>
+        </is>
+      </c>
+      <c r="G408" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="H408" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="I408" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="J408" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="K408" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="L408" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M408" s="6" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="N408" s="3" t="inlineStr"/>
+      <c r="O408" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="P408" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="Q408" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="R408" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S408" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="T408" s="3" t="inlineStr">
+        <is>
+          <t>Partially Verified</t>
+        </is>
+      </c>
+      <c r="U408" s="3" t="inlineStr">
+        <is>
+          <t>Amazon.in Marketplace</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U400"/>
+  <autoFilter ref="A1:U408"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
 </worksheet>

--- a/output/Amazon_Seller_Master_Data.xlsx
+++ b/output/Amazon_Seller_Master_Data.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Amazon Sellers" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Amazon Sellers'!$A$1:$U$408</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Amazon Sellers'!$A$1:$U$417</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U408"/>
+  <dimension ref="A1:U417"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -40092,8 +40092,881 @@
         </is>
       </c>
     </row>
+    <row r="409">
+      <c r="A409" s="3" t="inlineStr">
+        <is>
+          <t>Cutting Boards</t>
+        </is>
+      </c>
+      <c r="B409" s="3" t="inlineStr"/>
+      <c r="C409" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D409" s="3" t="inlineStr">
+        <is>
+          <t>E-COSMOS® LIFESTYLE LLP ⭐⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="E409" s="3" t="inlineStr">
+        <is>
+          <t>Marketplace Seller</t>
+        </is>
+      </c>
+      <c r="F409" s="3" t="inlineStr">
+        <is>
+          <t>Cutting Boards</t>
+        </is>
+      </c>
+      <c r="G409" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="H409" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="I409" s="3" t="inlineStr">
+        <is>
+          <t>contact@tollfreenumbers4u.com</t>
+        </is>
+      </c>
+      <c r="J409" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="K409" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="L409" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M409" s="6" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="N409" s="3" t="inlineStr"/>
+      <c r="O409" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="P409" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="Q409" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="R409" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S409" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="T409" s="3" t="inlineStr">
+        <is>
+          <t>Partially Verified</t>
+        </is>
+      </c>
+      <c r="U409" s="3" t="inlineStr">
+        <is>
+          <t>Amazon.in Marketplace</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="3" t="inlineStr">
+        <is>
+          <t>Finger Guards</t>
+        </is>
+      </c>
+      <c r="B410" s="3" t="inlineStr"/>
+      <c r="C410" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D410" s="3" t="inlineStr">
+        <is>
+          <t>Sheetal Traders...</t>
+        </is>
+      </c>
+      <c r="E410" s="3" t="inlineStr">
+        <is>
+          <t>Marketplace Seller</t>
+        </is>
+      </c>
+      <c r="F410" s="3" t="inlineStr">
+        <is>
+          <t>Finger Guards</t>
+        </is>
+      </c>
+      <c r="G410" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="H410" s="5" t="inlineStr">
+        <is>
+          <t>+917574884961</t>
+        </is>
+      </c>
+      <c r="I410" s="3" t="inlineStr">
+        <is>
+          <t>info@sheetaltrader.com</t>
+        </is>
+      </c>
+      <c r="J410" s="5" t="inlineStr">
+        <is>
+          <t>27AAZPR9243F1ZW</t>
+        </is>
+      </c>
+      <c r="K410" s="5" t="inlineStr">
+        <is>
+          <t>AAZPR9243F</t>
+        </is>
+      </c>
+      <c r="L410" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M410" s="6" t="inlineStr">
+        <is>
+          <t>shop no. 63, ratnakar business hub</t>
+        </is>
+      </c>
+      <c r="N410" s="3" t="inlineStr"/>
+      <c r="O410" s="3" t="inlineStr">
+        <is>
+          <t>ratnakar business hub</t>
+        </is>
+      </c>
+      <c r="P410" s="3" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="Q410" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="R410" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S410" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="T410" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U410" s="3" t="inlineStr">
+        <is>
+          <t>Amazon.in Marketplace</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="3" t="inlineStr">
+        <is>
+          <t>Finger Guards</t>
+        </is>
+      </c>
+      <c r="B411" s="3" t="inlineStr"/>
+      <c r="C411" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D411" s="3" t="inlineStr">
+        <is>
+          <t>FreshDcart®</t>
+        </is>
+      </c>
+      <c r="E411" s="3" t="inlineStr">
+        <is>
+          <t>Marketplace Seller</t>
+        </is>
+      </c>
+      <c r="F411" s="3" t="inlineStr">
+        <is>
+          <t>Finger Guards</t>
+        </is>
+      </c>
+      <c r="G411" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="H411" s="5" t="inlineStr">
+        <is>
+          <t>+919763002200</t>
+        </is>
+      </c>
+      <c r="I411" s="3" t="inlineStr">
+        <is>
+          <t>abhidukhande@gmail.com</t>
+        </is>
+      </c>
+      <c r="J411" s="5" t="inlineStr">
+        <is>
+          <t>06BPLPD6902H1Z0</t>
+        </is>
+      </c>
+      <c r="K411" s="5" t="inlineStr">
+        <is>
+          <t>BPLPD6902H</t>
+        </is>
+      </c>
+      <c r="L411" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M411" s="6" t="inlineStr">
+        <is>
+          <t>Lewa gujar samaj karyalay, shirsagar colony Hirawadi, apposite lane from green pharma NASHIK MAHARASHTRA India 422003, Maharashtra, Nashik, 422003</t>
+        </is>
+      </c>
+      <c r="N411" s="3" t="inlineStr"/>
+      <c r="O411" s="3" t="inlineStr">
+        <is>
+          <t>Nashik</t>
+        </is>
+      </c>
+      <c r="P411" s="3" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="Q411" s="5" t="inlineStr">
+        <is>
+          <t>422003</t>
+        </is>
+      </c>
+      <c r="R411" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S411" s="3" t="inlineStr">
+        <is>
+          <t>https://www.freshdcart.com/</t>
+        </is>
+      </c>
+      <c r="T411" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U411" s="3" t="inlineStr">
+        <is>
+          <t>Amazon.in Marketplace</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="3" t="inlineStr">
+        <is>
+          <t>Finger Guards</t>
+        </is>
+      </c>
+      <c r="B412" s="3" t="inlineStr"/>
+      <c r="C412" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D412" s="3" t="inlineStr">
+        <is>
+          <t>finistra</t>
+        </is>
+      </c>
+      <c r="E412" s="3" t="inlineStr">
+        <is>
+          <t>Marketplace Seller</t>
+        </is>
+      </c>
+      <c r="F412" s="3" t="inlineStr">
+        <is>
+          <t>Finger Guards</t>
+        </is>
+      </c>
+      <c r="G412" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="H412" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="I412" s="3" t="inlineStr">
+        <is>
+          <t>support@tofler.in</t>
+        </is>
+      </c>
+      <c r="J412" s="5" t="inlineStr">
+        <is>
+          <t>27AAPFU0939F1ZV</t>
+        </is>
+      </c>
+      <c r="K412" s="5" t="inlineStr">
+        <is>
+          <t>AAPFU0939F</t>
+        </is>
+      </c>
+      <c r="L412" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M412" s="6" t="inlineStr">
+        <is>
+          <t>vilnius, kirtimų g. 69, lt-02244</t>
+        </is>
+      </c>
+      <c r="N412" s="3" t="inlineStr"/>
+      <c r="O412" s="3" t="inlineStr">
+        <is>
+          <t>vilnius</t>
+        </is>
+      </c>
+      <c r="P412" s="3" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="Q412" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="R412" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S412" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="T412" s="3" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="U412" s="3" t="inlineStr">
+        <is>
+          <t>Amazon.in Marketplace</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="3" t="inlineStr">
+        <is>
+          <t>Finger Guards</t>
+        </is>
+      </c>
+      <c r="B413" s="3" t="inlineStr"/>
+      <c r="C413" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D413" s="3" t="inlineStr">
+        <is>
+          <t>Anzailala®</t>
+        </is>
+      </c>
+      <c r="E413" s="3" t="inlineStr">
+        <is>
+          <t>Marketplace Seller</t>
+        </is>
+      </c>
+      <c r="F413" s="3" t="inlineStr">
+        <is>
+          <t>Finger Guards</t>
+        </is>
+      </c>
+      <c r="G413" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="H413" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="I413" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="J413" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="K413" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="L413" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M413" s="6" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="N413" s="3" t="inlineStr"/>
+      <c r="O413" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="P413" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="Q413" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="R413" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S413" s="3" t="inlineStr">
+        <is>
+          <t>https://www.anzailala.com/</t>
+        </is>
+      </c>
+      <c r="T413" s="3" t="inlineStr">
+        <is>
+          <t>Partially Verified</t>
+        </is>
+      </c>
+      <c r="U413" s="3" t="inlineStr">
+        <is>
+          <t>Amazon.in Marketplace</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="3" t="inlineStr">
+        <is>
+          <t>Serving Sets</t>
+        </is>
+      </c>
+      <c r="B414" s="3" t="inlineStr"/>
+      <c r="C414" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D414" s="3" t="inlineStr">
+        <is>
+          <t>AAROYAA PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="E414" s="3" t="inlineStr">
+        <is>
+          <t>Marketplace Seller</t>
+        </is>
+      </c>
+      <c r="F414" s="3" t="inlineStr">
+        <is>
+          <t>Serving Sets</t>
+        </is>
+      </c>
+      <c r="G414" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="H414" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="I414" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="J414" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="K414" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="L414" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M414" s="6" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="N414" s="3" t="inlineStr"/>
+      <c r="O414" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="P414" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="Q414" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="R414" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S414" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="T414" s="3" t="inlineStr">
+        <is>
+          <t>Partially Verified</t>
+        </is>
+      </c>
+      <c r="U414" s="3" t="inlineStr">
+        <is>
+          <t>Amazon.in Marketplace</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="3" t="inlineStr">
+        <is>
+          <t>Disposable Spoons</t>
+        </is>
+      </c>
+      <c r="B415" s="3" t="inlineStr"/>
+      <c r="C415" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D415" s="3" t="inlineStr">
+        <is>
+          <t>RK World Infocom Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="E415" s="3" t="inlineStr">
+        <is>
+          <t>Marketplace Seller</t>
+        </is>
+      </c>
+      <c r="F415" s="3" t="inlineStr">
+        <is>
+          <t>Disposable Spoons</t>
+        </is>
+      </c>
+      <c r="G415" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="H415" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="I415" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="J415" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="K415" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="L415" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M415" s="6" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="N415" s="3" t="inlineStr"/>
+      <c r="O415" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="P415" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="Q415" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="R415" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S415" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="T415" s="3" t="inlineStr">
+        <is>
+          <t>Partially Verified</t>
+        </is>
+      </c>
+      <c r="U415" s="3" t="inlineStr">
+        <is>
+          <t>Amazon.in Marketplace</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="3" t="inlineStr">
+        <is>
+          <t>Hair Perms &amp; Texturizers</t>
+        </is>
+      </c>
+      <c r="B416" s="3" t="inlineStr"/>
+      <c r="C416" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D416" s="3" t="inlineStr">
+        <is>
+          <t>Bharatgaurav Enterprises</t>
+        </is>
+      </c>
+      <c r="E416" s="3" t="inlineStr">
+        <is>
+          <t>Marketplace Seller</t>
+        </is>
+      </c>
+      <c r="F416" s="3" t="inlineStr">
+        <is>
+          <t>Hair Perms &amp; Texturizers</t>
+        </is>
+      </c>
+      <c r="G416" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="H416" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="I416" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="J416" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="K416" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="L416" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M416" s="6" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="N416" s="3" t="inlineStr"/>
+      <c r="O416" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="P416" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="Q416" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="R416" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S416" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="T416" s="3" t="inlineStr">
+        <is>
+          <t>Partially Verified</t>
+        </is>
+      </c>
+      <c r="U416" s="3" t="inlineStr">
+        <is>
+          <t>Amazon.in Marketplace</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="3" t="inlineStr">
+        <is>
+          <t>Lips</t>
+        </is>
+      </c>
+      <c r="B417" s="3" t="inlineStr"/>
+      <c r="C417" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D417" s="3" t="inlineStr">
+        <is>
+          <t>RK World Infocom Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="E417" s="3" t="inlineStr">
+        <is>
+          <t>Seller</t>
+        </is>
+      </c>
+      <c r="F417" s="3" t="inlineStr">
+        <is>
+          <t>Lips</t>
+        </is>
+      </c>
+      <c r="G417" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="H417" s="5" t="inlineStr">
+        <is>
+          <t>+912012065294</t>
+        </is>
+      </c>
+      <c r="I417" s="3" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="J417" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="K417" s="5" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="L417" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M417" s="6" t="inlineStr">
+        <is>
+          <t>L-248, 2nd Floor, 17th Cross, Sector 6, HSR Layout, Bengaluru, Karnataka 560102. CIN: L72200KA2012PLC065294.</t>
+        </is>
+      </c>
+      <c r="N417" s="3" t="inlineStr"/>
+      <c r="O417" s="3" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="P417" s="3" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="Q417" s="5" t="inlineStr">
+        <is>
+          <t>560102</t>
+        </is>
+      </c>
+      <c r="R417" s="3" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="S417" s="3" t="inlineStr">
+        <is>
+          <t>https://tracxn.com/</t>
+        </is>
+      </c>
+      <c r="T417" s="3" t="inlineStr">
+        <is>
+          <t>Partially Verified</t>
+        </is>
+      </c>
+      <c r="U417" s="3" t="inlineStr">
+        <is>
+          <t>Amazon + Amazon.in Marketplace</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U408"/>
+  <autoFilter ref="A1:U417"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
 </worksheet>
